--- a/data_extactor/batch_10_fa/batch_0004_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0004_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن‌گفتن | گوش‌دادن فعال | درک مطلب | نگارش | استراتژی‌های یادگیری | یادگیری فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | آموزش و تربیت | مدیریت و سازماندهی | زبان انگلیسی | امنیت و ایمنی عمومی | روان‌شناسی | پرسنل و منابع انسانی | فروش و بازاریابی | اداری | ریاضیات | اقتصاد و حسابداری | کامپیوتر و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | مدیریت و اداره | زبان انگلیسی | ایمنی و امنیت عمومی | روان‌شناسی | پرسنل و منابع انسانی | فروش و بازاریابی | اداری | ریاضیات | اقتصاد و حسابداری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان کتبی | بیان شفاهی | استدلال قیاسی | درک شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی به اطلاعات | بینایی نزدیک | روان بودن ایده‌ها | اصالت | بینایی دور | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | حفظ‌کردن</t>
+          <t>بیان کتبی | بیان شفاهی | استدلال قیاسی | درک شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | روانی ایده‌ها | اصالت | بینایی دور | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | حفظ کردن</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | مکالمات تلفنی | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | ایمیل | پیامدها و نتایج کاری سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا منظم بودن | داخل ساختمان، با دمای کنترل‌شده | نزدیکی فیزیکی | فشار زمانی | پیامد اشتباه | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | موقعیت‌های تعارض | اهمیت تکرار وظایف مشابه | صرف زمان به صورت نشسته</t>
+          <t>ارتباط با دیگران | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | پیامدهای کاری و نتایج سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | نزدیکی فیزیکی | فشار زمانی | پیامد خطا | تعامل با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | اهمیت تکرار وظایف یکسان | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>معلمان آموزش فنی و حرفه‌ای، دوره متوسطه اول | کارکنان مراقبت از کودکان | مدیران آموزشی، مهدکودک تا دبیرستان | مدیران آموزشی، پس از متوسطه | مشاوران و راهنمایان تحصیلی، شغلی و تربیتی | معلمان دبستان، به جز آموزش استثنایی | متخصصان آموزش سلامت | هماهنگ‌کنندگان آموزشی | معلمان مهدکودک، به جز آموزش استثنایی | تحلیلگران مدیریت | مدیران خدمات پزشکی و سلامت | معلمان پیش‌دبستانی، به جز آموزش استثنایی | مدیران خدمات اجتماعی و جامعه | معلمان آموزش استثنایی، دبستان | معلمان آموزش استثنایی، مهدکودک | معلمان آموزش استثنایی، دوره متوسطه اول | معلمان آموزش استثنایی، دوره متوسطه دوم | دستیاران آموزشی، پیش‌دبستانی، دبستان، متوسطه اول و دوم، به جز آموزش استثنایی | مدیران آموزش و توسعه | متخصصان آموزش و توسعه</t>
+          <t>معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مربیان و کارکنان مراقبت از کودکان | مدیران آموزشی، مهدکودک تا دبیرستان | مدیران آموزشی، پس از متوسطه | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | متخصصان آموزش بهداشت | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | تحلیل‌گران مدیریت | مدیران خدمات پزشکی و بهداشتی | مربیان پیش‌دبستانی، به استثنای آموزش استثنایی | مدیران خدمات اجتماعی و جامعه | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | مدیران آموزش و توسعه | متخصصان آموزش و توسعه</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن‌گفتن | گوش‌دادن فعال | استراتژی‌های یادگیری | تفکر انتقادی | درک مطلب | نگارش | نظارت | یادگیری فعال | ریاضیات</t>
+          <t>سخن گفتن | گوش دادن فعال | راهبردهای یادگیری | تفکر انتقادی | درک مطلب | نگارش | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>آموزش و تربیت | مدیریت و سازماندهی | زبان انگلیسی | اداری | ریاضیات | خدمات مشتریان و شخصی | پرسنل و منابع انسانی | کامپیوتر و الکترونیک | روان‌شناسی | امنیت و ایمنی عمومی | ارتباطات و رسانه</t>
+          <t>آموزش و پرورش | مدیریت و اداره | زبان انگلیسی | اداری | ریاضیات | خدمات مشتری و شخصی | پرسنل و منابع انسانی | رایانه و الکترونیک | روان‌شناسی | ایمنی و امنیت عمومی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | استدلال قیاسی | بیان کتبی | تشخیص گفتار | حساسیت به مسئله | استدلال استقرایی | روان بودن ایده‌ها | ترتیب‌دهی به اطلاعات | بینایی نزدیک | اصالت | انعطاف‌پذیری دسته‌بندی | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار | سرعت بستار | استدلال ریاضی | اشتراک زمانی | حفظ‌کردن</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | استدلال قیاسی | بیان کتبی | تشخیص گفتار | حساسیت به مسئله | استدلال استقرایی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | بینایی نزدیک | اصالت | انعطاف‌پذیری دسته‌بندی | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار | سرعت بستار | استدلال ریاضی | تقسیم توجه | حفظ کردن</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | پیامدها و نتایج کاری سایر کارکنان | مکالمات تلفنی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | داخل ساختمان، با دمای کنترل‌شده | صرف زمان به صورت ایستاده | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | نزدیکی فیزیکی | سلامت و ایمنی سایر کارکنان | موقعیت‌های تعارض | صرف زمان به صورت پیاده‌روی یا دویدن</t>
+          <t>ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | پیامدهای کاری و نتایج سایر کارکنان | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نزدیکی فیزیکی | سلامت و ایمنی سایر کارکنان | موقعیت‌های تعارض | صرف زمان برای راه رفتن یا دویدن</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش فنی و حرفه‌ای، دوره متوسطه اول | مدیران آموزشی، پس از متوسطه | معلمان آموزش، پس از متوسطه | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان تحصیلی، شغلی و تربیتی | معلمان دبستان، به جز آموزش استثنایی | هماهنگ‌کنندگان آموزشی | معلمان مهدکودک، به جز آموزش استثنایی | معلمان دوره متوسطه اول، به جز آموزش استثنایی و فنی و حرفه‌ای | روان‌شناسان مدرسه | معلمان دبیرستان، به جز آموزش استثنایی و فنی و حرفه‌ای | معلمان آموزش استثنایی، دبستان | معلمان آموزش استثنایی، مهدکودک | معلمان آموزش استثنایی، دوره متوسطه اول | معلمان آموزش استثنایی، دوره متوسطه دوم | دستیاران آموزشی، پیش‌دبستانی، دبستان، متوسطه اول و دوم، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | مدیران آموزش و توسعه | مدرسان خصوصی</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مدیران آموزشی، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | روان‌شناسان مدرسه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | مدیران آموزش و توسعه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | سخن‌گفتن | نگارش | گوش‌دادن فعال | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | سخن گفتن | نگارش | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مدیریت و سازماندهی | آموزش و تربیت | خدمات مشتریان و شخصی | پرسنل و منابع انسانی | اداری | کامپیوتر و الکترونیک | ارتباطات و رسانه | ریاضیات | روان‌شناسی</t>
+          <t>زبان انگلیسی | مدیریت و اداره | آموزش و پرورش | خدمات مشتری و شخصی | پرسنل و منابع انسانی | اداری | رایانه و الکترونیک | ارتباطات و رسانه | ریاضیات | روان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | تشخیص گفتار | درک شفاهی | استدلال استقرایی | وضوح گفتار | اصالت | استدلال قیاسی | ترتیب‌دهی به اطلاعات | بینایی نزدیک | روان بودن ایده‌ها | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری بستار</t>
+          <t>درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | تشخیص گفتار | درک شفاهی | استدلال استقرایی | وضوح گفتار | اصالت | استدلال قیاسی | ترتیب‌دهی اطلاعات | بینایی نزدیک | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | داخل ساختمان، با دمای کنترل‌شده | تاثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا منظم بودن | پیامدها و نتایج کاری سایر کارکنان | فشار زمانی | صرف زمان به صورت نشسته | نامه‌ها و یادداشت‌های کتبی | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارکنان | فشار زمانی | صرف زمان برای نشستن | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>معلمان بازرگانی، پس از متوسطه | معلمان آموزش فنی و حرفه‌ای، دوره متوسطه اول | مدیران ارشد اجرایی | مدیران آموزشی، مهدکودک تا دبیرستان | معلمان آموزش، پس از متوسطه | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان تحصیلی، شغلی و تربیتی | معلمان علوم خانواده و مصرف‌کننده، پس از متوسطه | هماهنگ‌کنندگان آموزشی | معلمان کتابداری، پس از متوسطه | تحلیلگران مدیریت | مدیران خدمات پزشکی و سلامت | معلمان دوره متوسطه اول، به جز آموزش استثنایی و فنی و حرفه‌ای | معلمان دبیرستان، به جز آموزش استثنایی و فنی و حرفه‌ای | دستیاران پژوهشی علوم اجتماعی | معلمان مددکاری اجتماعی، پس از متوسطه | مدیران خدمات اجتماعی و جامعه | معلمان جامعه‌شناسی، پس از متوسطه | دستیاران آموزشی، پس از متوسطه | مدیران آموزش و توسعه</t>
+          <t>اساتید کسب‌وکار، پس از متوسطه | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مدیران ارشد اجرایی | مدیران آموزشی، مهدکودک تا دبیرستان | مدرسان علوم تربیتی، آموزش عالی | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | هماهنگ‌کنندگان آموزشی | مدرسان علوم کتابداری، آموزش عالی | تحلیل‌گران مدیریت | مدیران خدمات پزشکی و بهداشتی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | دستیاران تحقیقات علوم اجتماعی | مدرسان مددکاری اجتماعی، آموزش عالی | مدیران خدمات اجتماعی و جامعه | استادان جامعه‌شناسی، پس از متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | مدیران آموزش و توسعه</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش‌دادن فعال | سخن‌گفتن | نگارش | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>آموزش و تربیت | مدیریت و سازماندهی | پرسنل و منابع انسانی | زبان انگلیسی | خدمات مشتریان و شخصی | روان‌شناسی | قانون و حکومت | ارتباطات و رسانه | کامپیوتر و الکترونیک | جامعه‌شناسی و انسان‌شناسی</t>
+          <t>آموزش و پرورش | مدیریت و اداره | پرسنل و منابع انسانی | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | قانون و دولت | ارتباطات و رسانه | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی به اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روان بودن ایده‌ها | اصالت | توجه انتخابی | اشتراک زمانی | تجسم | حفظ‌کردن</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | داخل ساختمان، با دمای کنترل‌شده | صرف زمان به صورت نشسته | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا منظم بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | پیامدها و نتایج کاری سایر کارکنان | سخنرانی عمومی | موقعیت‌های تعارض | سطح رقابت</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | سخنرانی عمومی | موقعیت‌های تعارض | سطح رقابت</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدیران آموزشی، مهدکودک تا دبیرستان | مدیران آموزشی، پس از متوسطه | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | هماهنگ‌کنندگان آموزشی | مدیران آموزش و توسعه | متخصصان آموزش و توسعه | مدیران خدمات اجتماعی و جامعه | مدیران خدمات پزشکی و سلامت | مدیران عمومی و عملیاتی | مدیران خدمات اداری | مدیران منابع انسانی | مدیران ارشد اجرایی | افسران انطباق | تحلیلگران مدیریت | مدیران جمع‌آوری کمک‌های مالی | مدیران روابط عمومی | مشاوران و راهنمایان تحصیلی، شغلی و تربیتی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | معلمان پس از متوسطه، سایر | معلمان آموزش استثنایی، سایر</t>
+          <t>مدیران آموزشی، مهدکودک تا دبیرستان | مدیران آموزشی، پس از متوسطه | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | هماهنگ‌کنندگان آموزشی | مدیران آموزش و توسعه | متخصصان آموزش و توسعه | مدیران خدمات اجتماعی و جامعه | مدیران خدمات پزشکی و بهداشتی | مدیران عمومی و عملیات | مدیران خدمات اداری | مدیران منابع انسانی | مدیران ارشد اجرایی | افسران انطباق | تحلیل‌گران مدیریت | مدیران جمع‌آوری کمک‌های مالی | مدیران روابط عمومی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | اساتید پس از متوسطه، سایر موارد | معلمان آموزش ویژه، سایر موارد</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Adobe Acrobat Pro Extended | Adobe LifeCycle ES | Agile Product Lifecyle Management PLM | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | نرم‌افزار Amazon Web Services AWS | Ansible software | Apache Cassandra | Apache Groovy | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apple macOS | Aptean Made2Manage | Atlassian Confluence | Atlassian JIRA | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | Autodesk VIZ | Backbone.js | Bash | Bentley MicroStation | C | C# | C++ | Chef | Cisco IOS | نرم‌افزار رایانش ابری Citrix | نرم‌افزار طراحی و ترسیم به کمک کامپیوتر CADD | Customer information control system CICS | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Delcam PowerMILL | Django | Docker | نرم‌افزار طراحی و ترسیم | نرم‌افزار ESRI ArcGIS | ESRI ArcView | Elasticsearch | زبان نشانه‌گذاری گسترش‌پذیر XML | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Geometric CAMWorks | Git | GitHub | Go | HEC-1 | HEC-RAS | Hewlett Packard LoadRunner | Hewlett-Packard HP SolidDesigner | IBM Notes | IBM SPSS Statistics | JavaScript | JavaScript Object Notation JSON | Kronos Workforce Timekeeper | LAMP Stack | LSA Visual Easy Lean | Linux | نرم‌افزار زمان‌بندی تعمیر و نگهداری | MicroStrategy | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics NAV | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Word | Minitab | MongoDB | MySQL | Nagios | National Instruments LabVIEW | NoSQL | Node.js | Objective C | Open Mind hyperMILL | Oracle JD Edwards EnterpriseOne | Oracle Java | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | PHP | PTC Creo Parametric | Perforce Helix software | Perl | PostgreSQL | Puppet | Python | Qlik Tech QlikView | R | RTA Fleet Management | React | Realization Streamliner | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | Ruby | Ruby on Rails | نرم‌افزار SAP | Sage 50 Accounting | Scala | نرم‌افزار زمان‌بندی | Shell script | Splunk Enterprise | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Teradata Database | The Gordian Group PROGEN Online | The MathWorks MATLAB | Trimble SketchUp Pro | UNIX | Ubuntu | Verilog | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار گرادیان فشار سطح آب WSPG | نرم‌افزار مرورگر وب | Wireshark | نرم‌افزار جریان کار</t>
+          <t>Adobe Acrobat Pro Extended | Adobe LifeCycle ES | Agile Product Lifecyle Management PLM | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Cassandra | Apache Groovy | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apple macOS | Aptean Made2Manage | Atlassian Confluence | Atlassian JIRA | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | Autodesk VIZ | Backbone.js | Bash | Bentley MicroStation | C | C# | C++ | Chef | Cisco IOS | نرم‌افزار رایانش ابری Citrix | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | سیستم کنترل اطلاعات مشتری CICS | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Delcam PowerMILL | Django | Docker | نرم‌افزار ترسیم و طراحی | نرم‌افزار ESRI ArcGIS | ESRI ArcView | Elasticsearch | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Geometric CAMWorks | Git | GitHub | Go | HEC-1 | HEC-RAS | Hewlett Packard LoadRunner | Hewlett-Packard HP SolidDesigner | IBM Notes | IBM SPSS Statistics | JavaScript | JavaScript Object Notation JSON | Kronos Workforce Timekeeper | LAMP Stack | LSA Visual Easy Lean | Linux | نرم‌افزار زمان‌بندی تعمیر و نگهداری | MicroStrategy | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics NAV | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Word | Minitab | MongoDB | MySQL | Nagios | National Instruments LabVIEW | NoSQL | Node.js | Objective C | Open Mind hyperMILL | Oracle JD Edwards EnterpriseOne | Oracle Java | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | PHP | PTC Creo Parametric | نرم‌افزار Perforce Helix | Perl | PostgreSQL | Puppet | Python | Qlik Tech QlikView | R | RTA Fleet Management | React | Realization Streamliner | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | Ruby | Ruby on Rails | نرم‌افزار SAP | Sage 50 Accounting | Scala | نرم‌افزار زمان‌بندی | Shell script | Splunk Enterprise | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Teradata Database | The Gordian Group PROGEN Online | The MathWorks MATLAB | Trimble SketchUp Pro | UNIX | Ubuntu | Verilog | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار گرادیان فشار سطح آب WSPG | نرم‌افزار مرورگر وب | Wireshark | نرم‌افزار جریان کار</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن‌گفتن | نگارش | گوش‌دادن فعال | ریاضیات | تفکر انتقادی | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | ریاضیات | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>طراحی | مهندسی و فناوری | ریاضیات | مدیریت و سازماندهی | زبان انگلیسی | خدمات مشتریان و شخصی | مکانیک | کامپیوتر و الکترونیک | تولید و فرآوری | فیزیک | اداری | امنیت و ایمنی عمومی | ساختمان و ساخت‌وساز</t>
+          <t>طراحی | مهندسی و فناوری | ریاضیات | مدیریت و اداره | زبان انگلیسی | خدمات مشتری و شخصی | مکانیک | رایانه و الکترونیک | تولید و فرآوری | فیزیک | اداری | ایمنی و امنیت عمومی | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | بیان شفاهی | وضوح گفتار | استدلال ریاضی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | تجسم | روان بودن ایده‌ها | ترتیب‌دهی به اطلاعات | اصالت | سهولت کار با اعداد | بینایی دور | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | تشخیص رنگ‌های بصری</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | وضوح گفتار | استدلال ریاضی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | تجسم | روانی ایده‌ها | ترتیب‌دهی اطلاعات | اصالت | توانایی عددی | بینایی دور | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | ارتباط با دیگران | آزادی در تصمیم‌گیری | داخل ساختمان, با دمای کنترل‌شده | تعیین وظایف، اولویت‌ها و اهداف | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | پیامدها و نتایج کاری سایر کارکنان | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا منظم بودن | فراوانی تصمیم‌گیری | صرف زمان به صورت نشسته | فشار زمانی</t>
+          <t>ایمیل | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | صرف زمان برای نشستن | فشار زمانی</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>نقشه‌کشان معماری و عمران | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | تکنولوژیست‌ها و تکنسین‌های مهندسی عمران | مهندسان عمران | مدیران ساخت‌وساز | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | معلمان مهندسی، پس از متوسطه | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک | مهندسان تولید | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مدیران علوم طبیعی | متخصصان مدیریت پروژه | مهندسان فروش</t>
+          <t>نقشه‌کشان معماری و عمران | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | مدیران ساخت‌وساز | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | مدرسان مهندسی، پس از متوسطه | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک | مهندسان تولید | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مدیران علوم طبیعی | متخصصان مدیریت پروژه | مهندسان فروش</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ab Initio | Adobe Illustrator | Agilent ChemStation | Dassault Systemes CATIA | نرم‌افزار ایمیل | Epic Systems | Fleet Asset Management and Optimization Solutions FAMOS PEPSE | مترجم فرمول FORTRAN | نرم‌افزار حسابداری صندوق | GE Energy GateCycle | Linux | Microsoft Dynamics | Microsoft Excel | Microsoft Great Plains Personal Data Keeper | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft Visio | Microsoft Word | National Instruments LabVIEW | Oracle Java | Oracle Primavera Enterprise Project Portfolio Management | Perl | Python | نرم‌افزار SAP | SQL | UNIX | نرم‌افزار مرورگر وب</t>
+          <t>Ab Initio | Adobe Illustrator | Agilent ChemStation | Dassault Systemes CATIA | نرم‌افزار ایمیل | Epic Systems | Fleet Asset Management and Optimization Solutions FAMOS PEPSE | Formula translation/translator FORTRAN | نرم‌افزار حسابداری صندوق | GE Energy GateCycle | Linux | Microsoft Dynamics | Microsoft Excel | Microsoft Great Plains Personal Data Keeper | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft Visio | Microsoft Word | National Instruments LabVIEW | Oracle Java | Oracle Primavera Enterprise Project Portfolio Management | Perl | Python | نرم‌افزار SAP | زبان پرس‌وجوی ساختاریافته SQL | UNIX | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | سخن‌گفتن | تفکر انتقادی | گوش‌دادن فعال | نظارت | یادگیری فعال | ریاضیات | علوم تجربی</t>
+          <t>درک مطلب | نگارش | سخن گفتن | تفکر انتقادی | گوش دادن فعال | نظارت | یادگیری فعال | ریاضیات | علوم</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | شیمی | مهندسی و فناوری | ریاضیات | تولید و فرآوری | کامپیوتر و الکترونیک | مکانیک | مدیریت و سازماندهی</t>
+          <t>زبان انگلیسی | شیمی | مهندسی و فناوری | ریاضیات | تولید و فرآوری | رایانه و الکترونیک | مکانیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | درک کتبی | ترتیب‌دهی به اطلاعات | بیان کتبی | بیان شفاهی | استدلال استقرایی | اصالت | بینایی نزدیک | توجه انتخابی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | روان بودن ایده‌ها | سهولت کار با اعداد | انعطاف‌پذیری بستار | بینایی دور</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | بیان کتبی | بیان شفاهی | استدلال استقرایی | اصالت | بینایی نزدیک | توجه انتخابی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | توانایی عددی | انعطاف‌پذیری بستار | بینایی دور</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | داخل ساختمان، با دمای کنترل‌شده | اهمیت دقیق یا منظم بودن | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | پیامدها و نتایج کاری سایر کارکنان | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | مهندسان زیستی و زیست‌پزشکی | تکنسین‌های فرآوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان شیمی | مهندسان انرژی، به جز باد و خورشید | مهندسان پیل سوختی | مدیران تولید زمین‌گرمایی | مدیران تولید برق‌آبی | اکولوژیست‌های صنعتی | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید | مهندسان نانوسیستم‌ها | تکنولوژیست‌ها و تکنسین‌های مهندسی فناوری نانو | مهندسان سیستم‌های انرژی خورشیدی | مهندسان آب و فاضلاب | مدیران توسعه انرژی بادی</t>
+          <t>مهندسان کشاورزی | مهندسان زیستی و مهندسان زیست‌پزشکی | تکنسین‌های فرآوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان شیمی | مهندسان انرژی، به جز باد و خورشید | مهندسان پیل سوختی | مدیران تولید زمین‌گرمایی | مدیران تولید برق‌آبی | بوم‌شناسان صنعتی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان تولید | مهندسان نانوسیستم | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | مهندسان سیستم‌های انرژی خورشیدی | مهندسان آب و فاضلاب | مدیران توسعه انرژی بادی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | سخن‌گفتن | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | استراتژی‌های یادگیری | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | مدیریت و سازماندهی | تولید غذا | زبان انگلیسی | پرسنل و منابع انسانی | فروش و بازاریابی | ریاضیات | اداری | تولید و فرآوری | آموزش و تربیت | اقتصاد و حسابداری</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | تولید مواد غذایی | زبان انگلیسی | پرسنل و منابع انسانی | فروش و بازاریابی | ریاضیات | اداری | تولید و فرآوری | آموزش و پرورش | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | توجه انتخابی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی به اطلاعات | بینایی دور | زبردستی دستی | سهولت کار با اعداد | استدلال استقرایی | بیان کتبی</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | توجه انتخابی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بینایی دور | مهارت دستی | توانایی عددی | استدلال استقرایی | بیان کتبی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>کار با یا مشارکت در یک گروه کاری یا تیم | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | ارتباط با دیگران | داخل ساختمان، با دمای کنترل‌شده | مکالمات تلفنی | پیامدها و نتایج کاری سایر کارکنان | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | صرف زمان به صورت ایستاده | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | صرف زمان به صورت پیاده‌روی یا دویدن | اهمیت دقیق یا منظم بودن | فشار زمانی | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | موقعیت‌های تعارض | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات</t>
+          <t>کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | پیامدهای کاری و نتایج سایر کارکنان | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای ایستادن | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | صرف زمان برای راه رفتن یا دویدن | اهمیت دقیق یا درست بودن | فشار زمانی | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>نانوایان | قصابان و قطعه‌کنندگان گوش | سرآشپزها و آشپزهای ارشد | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای خانگی | آشپزهای رستوران | آشپزهای سفارش‌های سریع | تکنسین‌های رژیم غذایی | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | کارکنان فست‌فود و پیشخوان | سرپرستان خط اول کارکنان تهیه و سرو غذا | سرپرستان خط اول کارکنان خانه‌داری و خدمات نظافتی | سرپرستان خط اول کارکنان خدمات شخصی | سرپرستان خط اول کارکنان فروش خرده‌فروشی | کارکنان تهیه غذا | دانشمندان و تکنولوژیست‌های مواد غذایی | سروکنندگان غذا، غیررستورانی | میزبانان رستوران، سالن و کافی‌شاپ | پیشخدمت‌ها</t>
+          <t>نانوایان | قصابان و برش‌دهندگان گوش | سرآشپزها و آشپزهای ارشد | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | تکنسین‌های رژیم غذایی | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | کارگران فست فود و پیشخوان | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان رده اول کارکنان فروش خرده‌فروشی | کارگران آماده‌سازی مواد غذایی | دانشمندان و تکنولوژیست‌های علوم غذایی | سروکنندگان غذا، غیررستورانی | میزبانان رستوران، سالن و کافی‌شاپ | پیشخدمت‌ها و گارسون‌ها</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن‌گفتن | نظارت | گوش‌دادن فعال | نگارش | درک مطلب | یادگیری فعال | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | سخن گفتن | نظارت | گوش دادن فعال | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | مدیریت و سازماندهی | ریاضیات | پرسنل و منابع انسانی | اداری | کامپیوتر و الکترونیک | اقتصاد و حسابداری | آموزش و تربیت | امنیت و ایمنی عمومی | قانون و حکومت | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | ریاضیات | پرسنل و منابع انسانی | اداری | رایانه و الکترونیک | اقتصاد و حسابداری | آموزش و پرورش | ایمنی و امنیت عمومی | قانون و دولت | روان‌شناسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | ترتیب‌دهی به اطلاعات | بیان کتبی | درک کتبی | بینایی دور | انعطاف‌پذیری دسته‌بندی | سهولت کار با اعداد | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | سرعت بستار | اشتراک زمانی | استدلال ریاضی | روان بودن ایده‌ها</t>
+          <t>بیان شفاهی | درک شفاهی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | ترتیب‌دهی اطلاعات | بیان کتبی | درک کتبی | بینایی دور | انعطاف‌پذیری دسته‌بندی | توانایی عددی | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | سرعت بستار | تقسیم توجه | استدلال ریاضی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | داخل ساختمان، با دمای کنترل‌شده | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | فراوانی تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا منظم بودن | ایمیل | تاثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | تلفن همراه | تعیین وظایف، اولویت‌ها و اهداف | پیامدها و نتایج کاری سایر کارکنان | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | موقعیت‌های تعارض | فشار زمانی | نزدیکی فیزیکی | اهمیت تکرار وظایف مشابه | نامه‌ها و یادداشت‌های کتبی | پیامد اشتباه</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض | فشار زمانی | نزدیکی فیزیکی | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | پیامد خطا</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>متصدیان تفریح و سرگرمی | ورزشکاران و رقابت‌کنندگان ورزشی | صندوق‌داران | تعمیرکاران و سرویس‌کاران دستگاه‌های سکه‌ای، فروش خودکار و تفریحی | کاربران ورود داده‌ها | مدیران مالی | سرپرستان خط اول کارکنان خدمات قماربازی | سرپرستان خط اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | مدیران خدمات غذایی | کارکنان قفس کازینو | تعویض‌کنندگان پول قمار و صندوق‌داران غرفه | دیلرهای قماربازی | ماموران نظارت بر قمار و بازرسان قمار | نویسندگان و دوندگان شرط‌بندی ورزشی و قمار | مدیران عمومی و عملیاتی | میزبانان رستوران، سالن و کافی‌شاپ | مدیران اقامتی | تحویل‌داران بانک | داوران و سایر مقامات ورزشی</t>
+          <t>متصدیان تفریح و سرگرمی | ورزشکاران و رقبای ورزشی | صندوق‌داران | سرویس‌کاران و تعمیرکاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | اپراتورهای ورود داده | مدیران مالی | سرپرستان خط اول کارگران خدمات قمار | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | مدیران خدمات غذایی | کارکنان باجه قمارخانه | صندوق‌داران غرفه و مسئولان پول خرد قماربازی | دیلرهای قمار | ماموران نظارت بر قمار و بازرسان قمار | نویسندگان و دوندگان دفاتر شرط‌بندی ورزشی و قمار | مدیران عمومی و عملیات | میزبانان رستوران، سالن و کافی‌شاپ | مدیران اقامتی | تحویل‌داران | داوران، قضاوت‌کنندگان و سایر مقامات ورزشی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | سخن‌گفتن | تفکر انتقادی | درک مطلب | نگارش | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | آموزش و تربیت | زبان انگلیسی | مدیریت و سازماندهی | کامپیوتر و الکترونیک | امنیت و ایمنی عمومی | پرسنل و منابع انسانی | اداری | ریاضیات | جامعه‌شناسی و انسان‌شناسی | روان‌شناسی | ارتباطات و رسانه | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | اداری | ریاضیات | جامعه‌شناسی و انسان‌شناسی | روان‌شناسی | ارتباطات و رسانه | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | بیان کتبی | وضوح گفتار | حساسیت به مسئله | درک کتبی | بینایی نزدیک | استدلال استقرایی | استدلال قیاسی | روان بودن ایده‌ها | اصالت | ترتیب‌دهی به اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | بیان کتبی | وضوح گفتار | حساسیت به مسئله | درک کتبی | بینایی نزدیک | استدلال استقرایی | استدلال قیاسی | روانی ایده‌ها | اصالت | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | کار با یا مشارکت در یک گروه کاری یا تیم | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | داخل ساختمان، با دمای کنترل‌شده | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | تلفن همراه | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | سخنرانی عمومی | پیامدها و نتایج کاری سایر کارکنان</t>
+          <t>ایمیل | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | سخنرانی عمومی | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متصدیان تفریح و سرگرمی | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مربیان ورزشی و تناسب اندام گروهی | مدیران تسهیلات | سرپرستان خط اول کارکنان سرگرمی و تفریح، به جز خدمات قماربازی | سرپرستان خط اول کارکنان خدمات شخصی | هماهنگ‌کنندگان تناسب اندام و سلامت | مدیران عمومی و عملیاتی | مدیران اقامتی | تحلیلگران مدیریت | برنامه‌ریزان جلسات، کنوانسیون‌ها و رویدادها | طبیعی‌دانان پارک | کارکنان تفریحی | معلمان مطالعات تفریحی و تناسب اندام، پس از متوسطه | درمانگران تفریحی | معلمان خودشکوفایی | مدیران خدمات اجتماعی و جامعه | راهنمایان تور و همراهان | متخصصان آموزش و توسعه | راهنمایان مسافرتی</t>
+          <t>متصدیان تفریح و سرگرمی | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مربیان ورزشی و مدرسان تناسب اندام گروهی | مدیران تسهیلات | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارگران خدمات شخصی | هماهنگ‌کنندگان تناسب اندام و سلامتی | مدیران عمومی و عملیات | مدیران اقامتی | تحلیل‌گران مدیریت | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | طبیعت‌شناسان پارک | کارکنان تفریحات | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | درمانگران تفریحی | معلمان خودسازی | مدیران خدمات اجتماعی و جامعه | راهنمایان تور و همراهان | متخصصان آموزش و توسعه | راهنمایان سفر</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | سخن‌گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مدیریت و سازماندهی | پرسنل و منابع انسانی | خدمات مشتریان و شخصی | ریاضیات | فروش و بازاریابی | اداری | کامپیوتر و الکترونیک | اقتصاد و حسابداری | امنیت و ایمنی عمومی | آموزش و تربیت | ارتباطات و رسانه | روان‌شناسی</t>
+          <t>زبان انگلیسی | مدیریت و اداره | پرسنل و منابع انسانی | خدمات مشتری و شخصی | ریاضیات | فروش و بازاریابی | اداری | رایانه و الکترونیک | اقتصاد و حسابداری | ایمنی و امنیت عمومی | آموزش و پرورش | ارتباطات و رسانه | روان‌شناسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | روان بودن ایده‌ها | استدلال قیاسی | استدلال استقرایی | اصالت | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری بستار</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | روانی ایده‌ها | استدلال قیاسی | استدلال استقرایی | اصالت | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>تلفن همراه | ایمیل | ارتباط با دیگران | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | پیامدها و نتایج کاری سایر کارکنان | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا منظم بودن | اهمیت تکرار وظایف مشابه | داخل ساختمان، با دمای کنترل‌شده | موقعیت‌های تعارض | سخنرانی عمومی | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | سطح رقابت</t>
+          <t>مکالمات تلفنی | ایمیل | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | محیط داخلی، دارای کنترل شرایط محیطی | موقعیت‌های تعارض | سخنرانی عمومی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | سطح رقابت</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | دربان‌ها | متصدیان باجه و اجاره | مدیران سرگرمی و تفریح، به جز قماربازی | مدیران تسهیلات | سرپرستان خط اول کارکنان سرگرمی و تفریح، به جز خدمات قماربازی | سرپرستان خط اول کارکنان خانه‌داری و خدمات نظافتی | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | سرپرستان خط اول کارکنان خدمات شخصی | مدیران خدمات غذایی | مدیران عمومی و عملیاتی | میزبانان رستوران، سالن و کافی‌شاپ | کارمندان پذیرش هتل، متل و اقامتگاه | متصدیان رختکن و اتاق پرو | برنامه‌ریزان جلسات، کنوانسیون‌ها و رویدادها | مدیران املاک، مستغلات و انجمن‌های جامعه | متصدیان پذیرش و اطلاعات | ماموران فروش بلیط و رزرواسیون و کارمندان سفر | مدیران اسپا | راهنمایان، متصدیان لابی و بلیط‌گیرها</t>
+          <t>مدیران خدمات اداری | کانسرج‌ها | کارمندان باجه و اجاره | مدیران سرگرمی و تفریح، به جز قماربازی | مدیران تسهیلات | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول کارگران خدمات شخصی | مدیران خدمات غذایی | مدیران عمومی و عملیات | میزبانان رستوران، سالن و کافی‌شاپ | کارمندان پذیرش هتل، متل و اقامتگاه | متصدیان رختکن، اتاق لباس و اتاق پرو | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | مدیران املاک، مستغلات و انجمن‌های اجتماعی | متصدیان پذیرش و کارمندان اطلاعات | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | مدیران اسپا | راهنماها، متصدیان لابی و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0004_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0004_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | آموزش و تدریس | مدیریت و امور اداری | زبان انگلیسی | ایمنی و امنیت عمومی | روان‌شناسی | امور پرسنلی و منابع انسانی | فروش و بازاریابی | امور اداری | ریاضیات | اقتصاد و حسابداری | کامپیوتر و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | مدیریت و اداره | زبان انگلیسی | ایمنی و امنیت عمومی | روان‌شناسی | پرسنل و منابع انسانی | فروش و بازاریابی | اداری | ریاضیات | اقتصاد و حسابداری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان کتبی | بیان شفاهی | استدلال قیاسی | درک شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | سیالی ایده‌ها | اصالت | دید دور | انعطاف‌پذیری طبقه‌بندی | توجه انتخابی | حافظه</t>
+          <t>بیان کتبی | بیان شفاهی | استدلال قیاسی | درک شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | روانی ایده‌ها | اصالت | بینایی دور | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | حفظ کردن</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>دبیران دوره‌های فنی و حرفه‌ای دوره اول متوسطه | مربیان و مراقبان کودک | مدیران مدارس ابتدایی و متوسطه | مدیران آموزش عالی | مشاوران تحصیلی، راهنمایی و شغلی | آموزگاران مدارس ابتدایی، به‌استثنای آموزش استثنایی | کارشناسان آموزش بهداشت | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | مربیان پیش‌دبستانی، به‌استثنای آموزش استثنایی | تحلیل‌گران مدیریت و بهبود فرایندها | مدیران خدمات درمانی و بهداشتی | مربیان آموزش مهدکودک و پیش‌دبستانی، به‌استثنای آموزش استثنایی | مدیران خدمات اجتماعی و رفاهی | معلمان آموزش استثنایی ابتدایی | معلمان آموزش استثنایی مهدکودک و پیش‌دبستانی | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره دوم متوسطه | کمک‌مربیان پیش‌دبستانی، ابتدایی و متوسطه، به‌استثنای آموزش استثنایی | مدیران آموزش و بهسازی منابع انسانی | کارشناسان آموزش و توسعه منابع انسانی</t>
+          <t>معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مربیان و مراقبان کودک | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدیران آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان آموزش بهداشت و ارتقای سلامت | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | کارشناسان تحلیل مدیریت و روش‌ها | مدیران خدمات درمانی و بهداشتی | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | مدیران خدمات اجتماعی و خدمات مردمی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | دبیران آموزش استثنایی دوره دوم متوسطه | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | راهبردهای یادگیری | تفکر انتقادی | درک مطلب | نگارش | نظارت | یادگیری فعال | ریاضیات</t>
+          <t>سخن گفتن | گوش دادن فعال | راهبردهای یادگیری | تفکر انتقادی | درک مطلب | نگارش | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | مدیریت و امور اداری | زبان انگلیسی | امور اداری | ریاضیات | خدمات مشتریان و خدمات فردی | امور پرسنلی و منابع انسانی | کامپیوتر و الکترونیک | روان‌شناسی | ایمنی و امنیت عمومی | ارتباطات و رسانه</t>
+          <t>آموزش و پرورش | مدیریت و اداره | زبان انگلیسی | اداری | ریاضیات | خدمات مشتری و شخصی | پرسنل و منابع انسانی | رایانه و الکترونیک | روان‌شناسی | ایمنی و امنیت عمومی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | استدلال قیاسی | بیان کتبی | تشخیص گفتار | حساسیت به مسئله | استدلال استقرایی | سیالی ایده‌ها | مرتب‌سازی اطلاعات | دید نزدیک | اصالت | انعطاف‌پذیری طبقه‌بندی | دید دور | توجه انتخابی | انعطاف‌پذیری بازشناسی الگو | سرعت بازشناسی الگو | استدلال ریاضی | تسهیم توجه | حافظه</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | استدلال قیاسی | بیان کتبی | تشخیص گفتار | حساسیت به مسئله | استدلال استقرایی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | بینایی نزدیک | اصالت | انعطاف‌پذیری دسته‌بندی | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار | سرعت بستار | استدلال ریاضی | تقسیم توجه | حفظ کردن</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدرسان آموزش پایه بزرگسالان، متوسطه بزرگسالان و زبان دوم | دبیران دوره‌های فنی و حرفه‌ای دوره اول متوسطه | مدیران آموزش عالی | استادان علوم تربیتی دانشگاه | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مشاوران تحصیلی، راهنمایی و شغلی | آموزگاران مدارس ابتدایی، به‌استثنای آموزش استثنایی | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | مربیان پیش‌دبستانی، به‌استثنای آموزش استثنایی | دبیران دوره اول متوسطه، به‌استثنای آموزش استثنایی و فنی‌حرفه‌ای | روان‌شناسان مدرسه | دبیران دوره دوم متوسطه، به‌استثنای آموزش استثنایی و فنی‌حرفه‌ای | معلمان آموزش استثنایی ابتدایی | معلمان آموزش استثنایی مهدکودک و پیش‌دبستانی | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره دوم متوسطه | کمک‌مربیان پیش‌دبستانی، ابتدایی و متوسطه، به‌استثنای آموزش استثنایی | کمک‌معلمان آموزش استثنایی | مدیران آموزش و بهسازی منابع انسانی | مدرسان خصوصی و جبرانی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدیران آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | روان‌شناسان مدارس | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | دبیران آموزش استثنایی دوره دوم متوسطه | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | مدیران آموزش و بهسازی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | سخن گفتن | نگارش | شنیدن فعال | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | سخن گفتن | نگارش | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مدیریت و امور اداری | آموزش و تدریس | خدمات مشتریان و خدمات فردی | امور پرسنلی و منابع انسانی | امور اداری | کامپیوتر و الکترونیک | ارتباطات و رسانه | ریاضیات | روان‌شناسی</t>
+          <t>زبان انگلیسی | مدیریت و اداره | آموزش و پرورش | خدمات مشتری و شخصی | پرسنل و منابع انسانی | اداری | رایانه و الکترونیک | ارتباطات و رسانه | ریاضیات | روان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | تشخیص گفتار | درک شفاهی | استدلال استقرایی | وضوح گفتار | اصالت | استدلال قیاسی | مرتب‌سازی اطلاعات | دید نزدیک | سیالی ایده‌ها | انعطاف‌پذیری طبقه‌بندی | توجه انتخابی | انعطاف‌پذیری بازشناسی الگو</t>
+          <t>درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | تشخیص گفتار | درک شفاهی | استدلال استقرایی | وضوح گفتار | اصالت | استدلال قیاسی | ترتیب‌دهی اطلاعات | بینایی نزدیک | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>استادان علوم بازرگانی دانشگاه | دبیران دوره‌های فنی و حرفه‌ای دوره اول متوسطه | مدیران عامل و ارشد اجرایی | مدیران مدارس ابتدایی و متوسطه | استادان علوم تربیتی دانشگاه | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مشاوران تحصیلی، راهنمایی و شغلی | استادان علوم خانواده و مدیریت خدمات رفاهی دانشگاه | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | استادان علوم کتابداری و اطلاع‌رسانی | تحلیل‌گران مدیریت و بهبود فرایندها | مدیران خدمات درمانی و بهداشتی | دبیران دوره اول متوسطه، به‌استثنای آموزش استثنایی و فنی‌حرفه‌ای | دبیران دوره دوم متوسطه، به‌استثنای آموزش استثنایی و فنی‌حرفه‌ای | کارشناسان پژوهشی علوم اجتماعی | استادان مددکاری اجتماعی دانشگاه | مدیران خدمات اجتماعی و رفاهی | استادان جامعه‌شناسی دانشگاه | دستیاران آموزشی و تدریس دانشگاه | مدیران آموزش و بهسازی منابع انسانی</t>
+          <t>استادان علوم اداری و مدیریت، آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدیران عامل و مدیران ارشد اجرایی | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مشاوران تحصیلی، شغلی و هدایت استعدادها | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان تحلیل مدیریت و روش‌ها | مدیران خدمات درمانی و بهداشتی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | مدیران خدمات اجتماعی و خدمات مردمی | استادان جامعه‌شناسی دانشگاه | دستیاران آموزشی در آموزش عالی | مدیران آموزش و بهسازی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | مدیریت و امور اداری | امور پرسنلی و منابع انسانی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | روان‌شناسی | حقوق و امور دولتی | ارتباطات و رسانه | کامپیوتر و الکترونیک | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>آموزش و پرورش | مدیریت و اداره | پرسنل و منابع انسانی | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | قانون و دولت | ارتباطات و رسانه | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | سیالی ایده‌ها | اصالت | توجه انتخابی | تسهیم توجه | تجسم فضایی | حافظه</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدیران مدارس ابتدایی و متوسطه | مدیران آموزش عالی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | مدیران آموزش و بهسازی منابع انسانی | کارشناسان آموزش و توسعه منابع انسانی | مدیران خدمات اجتماعی و رفاهی | مدیران خدمات درمانی و بهداشتی | مدیران عمومی و عملیاتی | مدیران خدمات اداری و پشتیبانی | مدیران منابع انسانی | مدیران عامل و ارشد اجرایی | کارشناسان انطباق با قوانین و مقررات | تحلیل‌گران مدیریت و بهبود فرایندها | مدیران جذب سرمایه و هدایای مردمی | مدیران روابط عمومی | مشاوران تحصیلی، راهنمایی و شغلی | کارشناسان کتابداری و آرشیو رسانه‌ای | استادان آموزش عالی، سایر رشته‌ها | معلمان آموزش استثنایی، سایر مقاطع</t>
+          <t>مدیران آموزشی مقاطع ابتدایی و متوسطه | مدیران آموزش عالی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی | مدیران خدمات اجتماعی و خدمات مردمی | مدیران خدمات درمانی و بهداشتی | مدیران کل و مدیران عملیات | مدیران خدمات اداری و پشتیبانی | مدیران منابع انسانی | مدیران عامل و مدیران ارشد اجرایی | کارشناسان پایش انطباق و بازرسی مقرراتی | کارشناسان تحلیل مدیریت و روش‌ها | مدیران جذب منابع مالی و حامیان | مدیران روابط عمومی | مشاوران تحصیلی، شغلی و هدایت استعدادها | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | سایر مدرسان در آموزش عالی | معلمان آموزش استثنایی، سایر عناوین</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | نگارش | شنیدن فعال | ریاضیات | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | ریاضیات | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>طراحی | فنی و مهندسی | ریاضیات | مدیریت و امور اداری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مکانیک | کامپیوتر و الکترونیک | تولید و فراوری | فیزیک | امور اداری | ایمنی و امنیت عمومی | ساختمان و سازه</t>
+          <t>طراحی | مهندسی و فناوری | ریاضیات | مدیریت و اداره | زبان انگلیسی | خدمات مشتری و شخصی | مکانیک | رایانه و الکترونیک | تولید و فرآوری | فیزیک | اداری | ایمنی و امنیت عمومی | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | بیان شفاهی | وضوح گفتار | استدلال ریاضی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | تجسم فضایی | سیالی ایده‌ها | مرتب‌سازی اطلاعات | اصالت | توانایی کار با اعداد | دید دور | انعطاف‌پذیری طبقه‌بندی | انعطاف‌پذیری بازشناسی الگو | توجه انتخابی | تمایز رنگی دیداری</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | وضوح گفتار | استدلال ریاضی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | تجسم | روانی ایده‌ها | ترتیب‌دهی اطلاعات | اصالت | توانایی عددی | بینایی دور | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>نقشه‌کش‌های معماری و عمران | مدیران توسعه محصول و فناوری زیست‌سوخت | تکنسین‌ها و کاردان‌های مهندسی عمران | مهندسان عمران | مدیران پروژه‌های عمرانی و ساخت‌وساز | مهندسان برق | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | نقشه‌کش‌های برق و الکترونیک | مهندسان الکترونیک، به‌استثنای کامپیوتر | استادان علوم مهندسی دانشگاه | تکنسین‌ها و کاردان‌های مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک و زنجیره تأمین | مهندسان تولید و ساخت | کاردان‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مدیران علوم طبیعی | کارشناسان مدیریت پروژه | مهندسان فروش و بازاریابی فنی</t>
+          <t>نقشه‌کشان معماری و عمران | مدیران توسعه محصول و فناوری زیست‌سوخت | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | مدیران پروژه‌های ساختمانی | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | استادان و مدرسان مهندسی در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک و زنجیره تأمین | مهندسان تولید و ساخت | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مدیران علوم طبیعی و پایه‌ای | کارشناسان مدیریت پروژه | مهندسان فروش</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | سخن گفتن | تفکر انتقادی | شنیدن فعال | نظارت | یادگیری فعال | ریاضیات | علوم تجربی</t>
+          <t>درک مطلب | نگارش | سخن گفتن | تفکر انتقادی | گوش دادن فعال | نظارت | یادگیری فعال | ریاضیات | علوم</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | شیمی | فنی و مهندسی | ریاضیات | تولید و فراوری | کامپیوتر و الکترونیک | مکانیک | مدیریت و امور اداری</t>
+          <t>زبان انگلیسی | شیمی | مهندسی و فناوری | ریاضیات | تولید و فرآوری | رایانه و الکترونیک | مکانیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات | بیان کتبی | بیان شفاهی | استدلال استقرایی | اصالت | دید نزدیک | توجه انتخابی | استدلال ریاضی | انعطاف‌پذیری طبقه‌بندی | وضوح گفتار | تشخیص گفتار | سیالی ایده‌ها | توانایی کار با اعداد | انعطاف‌پذیری بازشناسی الگو | دید دور</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | بیان کتبی | بیان شفاهی | استدلال استقرایی | اصالت | بینایی نزدیک | توجه انتخابی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | توانایی عددی | انعطاف‌پذیری بستار | بینایی دور</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | مهندسان زیستی و پزشکی | تکنسین‌های فراوری زیست‌سوخت | مدیران تولید زیست‌سوخت | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان شیمی | مهندسان انرژی، به‌استثنای بادی و خورشیدی | مهندسان پیل سوختی | مدیران تولید انرژی زمین‌گرمایی | مدیران تولید برق‌آبی | بوم‌شناسان صنعتی | تکنسین‌ها و کاردان‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | مهندسان نانوسیستم‌ها | کاردان‌ها و تکنسین‌های مهندسی فناوری نانو | مهندسان سیستم‌های انرژی خورشیدی | مهندسان آب و فاضلاب | مدیران توسعه انرژی بادی</t>
+          <t>مهندسان کشاورزی | مهندسان پزشکی و بیوانجینیرینگ | تکنسین‌های فراوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان شیمی | مهندسان انرژی، به‌جز بادی و خورشیدی | مهندسان پیل سوختی | مدیران تولید انرژی زمین‌گرمایی | مدیران تولید نیروگاه‌های برق‌آبی | بوم‌شناسان صنعتی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | مهندسان نانوسیستم‌ها | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | مهندسان سیستم‌های انرژی خورشیدی | مهندسان آب و فاضلاب | مدیران توسعه پروژه‌های انرژی بادی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | صنایع غذایی و تولید خوراک | زبان انگلیسی | امور پرسنلی و منابع انسانی | فروش و بازاریابی | ریاضیات | امور اداری | تولید و فراوری | آموزش و تدریس | اقتصاد و حسابداری</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | تولید مواد غذایی | زبان انگلیسی | پرسنل و منابع انسانی | فروش و بازاریابی | ریاضیات | اداری | تولید و فرآوری | آموزش و پرورش | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | دید نزدیک | توجه انتخابی | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | دید دور | چابکی دستی | توانایی کار با اعداد | استدلال استقرایی | بیان کتبی</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | توجه انتخابی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بینایی دور | مهارت دستی | توانایی عددی | استدلال استقرایی | بیان کتبی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>نانوایان | قصابان و قطعه‌کاران گوشت | سرآشپزان و آشپزان ارشد | آشپزان فست‌فود | آشپزان سازمانی و غذاخوری‌های بزرگ | آشپزان منازل مسکونی | آشپزان رستورانی | آشپزان غذاهای فوری | تکنسین‌های تغذیه و رژیم‌درمانی | کارگران خدمات پذیرایی، سلف‌سرویس و دستیاران باریستا | کارکنان پیشخوان و فست‌فود | سرپرستان رده اول کارگران آماده‌سازی و سرو غذا | سرپرستان رده اول خدمات خانه‌داری و نظافت | سرپرستان رده اول ارائه‌دهندگان خدمات فردی | سرپرستان رده اول فروشندگان خرده‌فروشی | کارگران آماده‌سازی غذا | دانشمندان و کارشناسان صنایع غذایی | مهمانداران و مهمان‌پذیران سالن | میزبانان رستوران، سالن و کافه | گارسون‌ها و پیشخدمت‌های رستوران</t>
+          <t>نانوایان و شیرینی‌پزان | قصابان و برش‌کاران گوشت | سرآشپزان و آشپزان ارشد | آشپزان غذاهای فوری و فست‌فود | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان منازل مسکونی و سرآشپزان شخصی | آشپزان رستوران | آشپزان غذاهای فوری | کاردان‌ها و تکنسین‌های تغذیه و رژیم‌درمانی | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده‌اول فروشندگان خرده‌فروشی | کارگران آماده‌سازی غذا | متخصصان و کارشناسان علوم و صنایع غذایی | سروکنندگان غذا در محیط‌های غیررستورانی | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نظارت | شنیدن فعال | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | سخن گفتن | نظارت | گوش دادن فعال | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | ریاضیات | امور پرسنلی و منابع انسانی | امور اداری | کامپیوتر و الکترونیک | اقتصاد و حسابداری | آموزش و تدریس | ایمنی و امنیت عمومی | حقوق و امور دولتی | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | ریاضیات | پرسنل و منابع انسانی | اداری | رایانه و الکترونیک | اقتصاد و حسابداری | آموزش و پرورش | ایمنی و امنیت عمومی | قانون و دولت | روان‌شناسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | مرتب‌سازی اطلاعات | بیان کتبی | درک کتبی | دید دور | انعطاف‌پذیری طبقه‌بندی | توانایی کار با اعداد | انعطاف‌پذیری بازشناسی الگو | توجه انتخابی | سرعت ادراک | سرعت بازشناسی الگو | تسهیم توجه | استدلال ریاضی | سیالی ایده‌ها</t>
+          <t>بیان شفاهی | درک شفاهی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | ترتیب‌دهی اطلاعات | بیان کتبی | درک کتبی | بینایی دور | انعطاف‌پذیری دسته‌بندی | توانایی عددی | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | سرعت بستار | تقسیم توجه | استدلال ریاضی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>خدمتگزاران و متصدیان اماکن تفریحی و شهربازی | ورزشکاران و قهرمانان ورزشی | صندوق‌داران | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و تفریحی | کاربران ثبت و ورود اطلاعات | مدیران مالی | سرپرستان رده اول کارکنان سالن‌های بازی و تفریحی | سرپرستان رده اول فروشندگان غیرخرده‌فروشی | سرپرستان رده اول پشتیبانی دفتری و اداری | مدیران خدمات پذیرایی و غذا و نوشیدنی | کارکنان باجه و دریافت صندوق بازی | کارکنان تبدیل ژتون و صندوق | مجریان و متصدیان بازی‌های رومیزی و کارتی | مأموران مراقبت سالن و ناظران بازی‌ها | ثبت‌کنندگان و متصدیان شرط‌بندی مسابقات ورزشی | مدیران عمومی و عملیاتی | میزبانان رستوران، سالن و کافه | مدیران اقامتی و هتلداری | باجه‌داران و تحویل‌داران بانکی | داوران و مسئولان برگزاری مسابقات ورزشی</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | ورزشکاران و قهرمانان حرفه‌ای | صندوق‌داران | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | متصدیان ورود اطلاعات و داده‌آمایی | مدیران امور مالی | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | مدیران خدمات پذیرایی و غذا و نوشیدنی | متصدیان باجه و خزانه‌داری مراکز بازی و سرگرمی | صندوق‌داران و متصدیان تبدیل ژتون و وجه در مراکز تفریحی | گردانندگان بازی‌های میزی و کازینویی | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | متصدیان ثبت و پرداخت شرط‌بندی‌های ورزشی و سرگرمی | مدیران کل و مدیران عملیات | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | مدیران هتل و مراکز اقامتی | تحویل‌داران و متصدیان امور بانکی | داوران و مسئولان مسابقات ورزشی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | آموزش و تدریس | زبان انگلیسی | مدیریت و امور اداری | کامپیوتر و الکترونیک | ایمنی و امنیت عمومی | امور پرسنلی و منابع انسانی | امور اداری | ریاضیات | جامعه‌شناسی و مردم‌شناسی | روان‌شناسی | ارتباطات و رسانه | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | اداری | ریاضیات | جامعه‌شناسی و انسان‌شناسی | روان‌شناسی | ارتباطات و رسانه | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | بیان کتبی | وضوح گفتار | حساسیت به مسئله | درک کتبی | دید نزدیک | استدلال استقرایی | استدلال قیاسی | سیالی ایده‌ها | اصالت | مرتب‌سازی اطلاعات | انعطاف‌پذیری طبقه‌بندی | توجه انتخابی</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | بیان کتبی | وضوح گفتار | حساسیت به مسئله | درک کتبی | بینایی نزدیک | استدلال استقرایی | استدلال قیاسی | روانی ایده‌ها | اصالت | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و شهربازی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مربیان بدنسازی و ورزش‌های گروهی | مدیران امور تأسیسات و ساختمان | سرپرستان رده اول ارائه‌دهندگان خدمات تفریحی و سرگرمی | سرپرستان رده اول ارائه‌دهندگان خدمات فردی | هماهنگ‌کنندگان خدمات تندرستی و سلامت | مدیران عمومی و عملیاتی | مدیران اقامتی و هتلداری | تحلیل‌گران مدیریت و بهبود فرایندها | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | کارشناسان حفاظت محیط‌زیست و پارکبان‌ها | کارکنان خدمات تفریحی و اوقات فراغت | مدرسان دانشگاهی تربیت‌بدنی و علوم ورزشی | کارشناسان درمان با بازی و فعالیت‌های تفریحی | مدرسان آزاد دوره‌های خودشکوفایی و هنری | مدیران خدمات اجتماعی و رفاهی | راهنمایان تور و گردشگری | کارشناسان آموزش و توسعه منابع انسانی | راهنمایان سفر و سیاحت</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مربیان ورزش و آمادگی جسمانی گروهی | مدیران امور ساختمان و تأسیسات | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | مدیران کل و مدیران عملیات | مدیران هتل و مراکز اقامتی | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | طبیعت‌شناسان و کارشناسان پارک‌های ملی | کارکنان و متصدیان امور تفریحی و اوقات فراغت | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | کارشناسان تفریح‌درمانی | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | مدیران خدمات اجتماعی و خدمات مردمی | راهنمایان تور و گردشگری | کارشناسان آموزش و توسعه منابع انسانی | راهنمایان گردشگری و تور</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مدیریت و امور اداری | امور پرسنلی و منابع انسانی | خدمات مشتریان و خدمات فردی | ریاضیات | فروش و بازاریابی | امور اداری | کامپیوتر و الکترونیک | اقتصاد و حسابداری | ایمنی و امنیت عمومی | آموزش و تدریس | ارتباطات و رسانه | روان‌شناسی</t>
+          <t>زبان انگلیسی | مدیریت و اداره | پرسنل و منابع انسانی | خدمات مشتری و شخصی | ریاضیات | فروش و بازاریابی | اداری | رایانه و الکترونیک | اقتصاد و حسابداری | ایمنی و امنیت عمومی | آموزش و پرورش | ارتباطات و رسانه | روان‌شناسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات | سیالی ایده‌ها | استدلال قیاسی | استدلال استقرایی | اصالت | استدلال ریاضی | انعطاف‌پذیری طبقه‌بندی | دید نزدیک | توجه انتخابی | انعطاف‌پذیری بازشناسی الگو</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | روانی ایده‌ها | استدلال قیاسی | استدلال استقرایی | اصالت | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری و پشتیبانی | مسئولان خدمات اختصاصی هتل (کانسیرژ) | متصدیان باجه و کرایه تجهیزات | مدیران مجموعه‌های تفریحی، ورزشی و رویدادها | مدیران امور تأسیسات و ساختمان | سرپرستان رده اول ارائه‌دهندگان خدمات تفریحی و سرگرمی | سرپرستان رده اول خدمات خانه‌داری و نظافت | سرپرستان رده اول پشتیبانی دفتری و اداری | سرپرستان رده اول ارائه‌دهندگان خدمات فردی | مدیران خدمات پذیرایی و غذا و نوشیدنی | مدیران عمومی و عملیاتی | میزبانان رستوران، سالن و کافه | متصدیان پذیرش هتل، متل و مراکز اقامتی | متصدیان رختکن، امانات و تعویض لباس | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | مدیران املاک، مستغلات و مجتمع‌های مسکونی | مسئولان پذیرش و دفاتر اطلاعات | متصدیان صدور بلیط، رزرواسیون و کارمندان آژانس‌های مسافرتی | مدیران مراکز ماساژ و آب‌درمانی | مسئولان کنترل سالن، راهنمایان لابی و بلیط‌گیرها</t>
+          <t>مدیران خدمات اداری و پشتیبانی | متصدیان تشریفات و خدمات میهمانان | متصدیان باجه و کرایه کالا و خدمات | مدیران مجموعه‌های تفریحی، ورزشی و رویدادها | مدیران امور ساختمان و تأسیسات | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | مدیران خدمات پذیرایی و غذا و نوشیدنی | مدیران کل و مدیران عملیات | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | متصدیان رختکن، امانات و اتاق پرو | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | مدیران املاک، مستغلات و مجتمع‌های مسکونی | متصدیان پذیرش و اطلاعات | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | مدیران مراکز خدمات اسپا و مراقبت‌های زیبایی | راهنماها، متصدیان سالن و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
